--- a/artfynd/A 39323-2024 artfynd.xlsx
+++ b/artfynd/A 39323-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY164"/>
+  <dimension ref="A1:AZ164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89150371</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89150372</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89643979</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89643981</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601374</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601375</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Inventering på Storön</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601376</t>
         </is>
       </c>
     </row>
@@ -1487,6 +1527,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92602428</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92609040</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034432</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601400</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1910,6 +1970,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601405</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2007,6 +2072,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89150374</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2104,6 +2174,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89150375</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2203,6 +2278,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Inventering på Storön</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601402</t>
         </is>
       </c>
     </row>
@@ -2310,6 +2390,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92625804</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2411,6 +2496,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601410</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2517,6 +2607,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92625075</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2623,6 +2718,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92625077</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2729,6 +2829,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92625082</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2835,6 +2940,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034383</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2941,6 +3051,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034393</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3047,6 +3162,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034395</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3144,6 +3264,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89150376</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3241,6 +3366,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89150373</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3342,6 +3472,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601379</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3443,6 +3578,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601380</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3544,6 +3684,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601381</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3645,6 +3790,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601388</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3746,6 +3896,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601398</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3843,6 +3998,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89150378</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3952,6 +4112,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92602792</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4061,6 +4226,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92602817</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4170,6 +4340,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92602832</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4271,6 +4446,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601404</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4384,6 +4564,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92602324</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4497,6 +4682,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92602357</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4610,6 +4800,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92602388</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4707,6 +4902,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89150383</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4804,6 +5004,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89150384</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4901,6 +5106,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89150385</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4998,6 +5208,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89150386</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5109,6 +5324,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89642622</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5220,6 +5440,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89642919</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5331,6 +5556,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89643965</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5436,6 +5666,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600012</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5541,6 +5776,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600013</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5646,6 +5886,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600014</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5751,6 +5996,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600015</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5856,6 +6106,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600017</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5961,6 +6216,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600018</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6066,6 +6326,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600019</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6171,6 +6436,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600020</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6276,6 +6546,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600022</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6381,6 +6656,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600023</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6486,6 +6766,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600024</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6591,6 +6876,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6696,6 +6986,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600026</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6801,6 +7096,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600027</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6906,6 +7206,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600028</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7011,6 +7316,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600036</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7116,6 +7426,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600037</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7221,6 +7536,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600038</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7326,6 +7646,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600039</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7431,6 +7756,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600040</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7536,6 +7866,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600041</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7641,6 +7976,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92600042</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7742,6 +8082,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601389</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7843,6 +8188,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601390</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7944,6 +8294,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601391</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8045,6 +8400,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601392</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8146,6 +8506,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601393</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8247,6 +8612,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601394</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8348,6 +8718,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601397</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8449,6 +8824,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92601399</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8559,6 +8939,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92608267</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8669,6 +9054,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92608268</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8779,6 +9169,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92608269</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8889,6 +9284,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92608270</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8999,6 +9399,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92608271</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9100,6 +9505,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621685</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9201,6 +9611,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621687</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9302,6 +9717,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621688</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9403,6 +9823,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621689</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9504,6 +9929,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621690</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9605,6 +10035,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621692</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9706,6 +10141,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621694</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9807,6 +10247,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621696</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9908,6 +10353,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621697</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10009,6 +10459,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621698</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10110,6 +10565,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621699</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10211,6 +10671,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621702</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10312,6 +10777,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621703</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10413,6 +10883,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621705</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10514,6 +10989,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621706</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10615,6 +11095,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621707</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10716,6 +11201,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621708</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10817,6 +11307,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621709</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10918,6 +11413,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92621710</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11024,6 +11524,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034385</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11130,6 +11635,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034386</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11236,6 +11746,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034387</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11342,6 +11857,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034389</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11448,6 +11968,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034390</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11554,6 +12079,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034391</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11660,6 +12190,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034394</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11766,6 +12301,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034396</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11872,6 +12412,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034397</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11978,6 +12523,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034398</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12084,6 +12634,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034399</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12190,6 +12745,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034400</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12296,6 +12856,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034402</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12402,6 +12967,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034403</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12508,6 +13078,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034404</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12614,6 +13189,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034405</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12720,6 +13300,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034406</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12826,6 +13411,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034407</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12932,6 +13522,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034409</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13038,6 +13633,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034412</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13144,6 +13744,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034413</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13250,6 +13855,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034414</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13356,6 +13966,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034416</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13462,6 +14077,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034417</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13568,6 +14188,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034418</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13674,6 +14299,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034420</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13780,6 +14410,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034421</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13886,6 +14521,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034423</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13992,6 +14632,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034424</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14098,6 +14743,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034426</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14204,6 +14854,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034427</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14310,6 +14965,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034428</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14416,6 +15076,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034429</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14522,6 +15187,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034430</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14628,6 +15298,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034433</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14734,6 +15409,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034434</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14840,6 +15520,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034435</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14946,6 +15631,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034436</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15052,6 +15742,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034437</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15158,6 +15853,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034438</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15264,6 +15964,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034439</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15370,6 +16075,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034440</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15476,6 +16186,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034441</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15582,6 +16297,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034445</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15688,6 +16408,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034446</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15794,6 +16519,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034448</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15900,6 +16630,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034449</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16006,6 +16741,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034450</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16112,6 +16852,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034451</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16218,6 +16963,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034453</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16324,6 +17074,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034454</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16430,6 +17185,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034455</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16536,6 +17296,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034457</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16642,6 +17407,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034458</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16748,6 +17518,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034459</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16854,6 +17629,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034460</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16960,6 +17740,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034461</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17066,6 +17851,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034462</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17172,6 +17962,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034464</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17278,6 +18073,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034465</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17384,6 +18184,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034466</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17490,6 +18295,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034467</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17596,6 +18406,11 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034468</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17702,8 +18517,178 @@
           <t>Inventering på Storön</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93034469</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>